--- a/data/data_raw/umweltbundesamt/Mio. t CO₂-Äquivalent nach Jahr und Sektor.xlsx
+++ b/data/data_raw/umweltbundesamt/Mio. t CO₂-Äquivalent nach Jahr und Sektor.xlsx
@@ -103,8 +103,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:C207">
-  <autoFilter ref="A3:C207"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A3:C213">
+  <autoFilter ref="A3:C213"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Jahr"/>
     <tableColumn id="2" name="Summe von Mio. t CO₂-Äquivalent"/>
@@ -439,7 +439,7 @@
         <v>1990</v>
       </c>
       <c s="7">
-        <v>4.65836317443853</v>
+        <v>4.85589537343917</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -450,7 +450,7 @@
         <v>1990</v>
       </c>
       <c s="7">
-        <v>36.4075385341994</v>
+        <v>36.5835032169962</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -472,7 +472,7 @@
         <v>1990</v>
       </c>
       <c s="7">
-        <v>12.918434658725</v>
+        <v>12.9184316550176</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -483,7 +483,7 @@
         <v>1990</v>
       </c>
       <c s="7">
-        <v>9.78509849151557</v>
+        <v>9.94951382765568</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -494,7 +494,7 @@
         <v>1990</v>
       </c>
       <c s="7">
-        <v>13.7632042778976</v>
+        <v>13.7638584284405</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -505,7 +505,7 @@
         <v>1991</v>
       </c>
       <c s="7">
-        <v>4.71461724827986</v>
+        <v>4.91385818479558</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -516,7 +516,7 @@
         <v>1991</v>
       </c>
       <c s="7">
-        <v>37.2809535514511</v>
+        <v>37.4570684030872</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -538,7 +538,7 @@
         <v>1991</v>
       </c>
       <c s="7">
-        <v>14.1421688234732</v>
+        <v>14.1421676198281</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -549,7 +549,7 @@
         <v>1991</v>
       </c>
       <c s="7">
-        <v>9.65826959977061</v>
+        <v>9.82915421188974</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -560,7 +560,7 @@
         <v>1991</v>
       </c>
       <c s="7">
-        <v>15.2419989726717</v>
+        <v>15.2427591754103</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -571,7 +571,7 @@
         <v>1992</v>
       </c>
       <c s="7">
-        <v>4.75969950861962</v>
+        <v>4.96043052761474</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -582,7 +582,7 @@
         <v>1992</v>
       </c>
       <c s="7">
-        <v>32.1986546221794</v>
+        <v>32.3744208312841</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -593,7 +593,7 @@
         <v>1992</v>
       </c>
       <c s="7">
-        <v>1.14004202735253</v>
+        <v>1.14004314776623</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -604,7 +604,7 @@
         <v>1992</v>
       </c>
       <c s="7">
-        <v>13.590600859472</v>
+        <v>13.5906010342794</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -615,7 +615,7 @@
         <v>1992</v>
       </c>
       <c s="7">
-        <v>9.27758285674143</v>
+        <v>9.44719334108927</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -626,7 +626,7 @@
         <v>1992</v>
       </c>
       <c s="7">
-        <v>15.2102964311674</v>
+        <v>15.2110605524073</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -637,7 +637,7 @@
         <v>1993</v>
       </c>
       <c s="7">
-        <v>4.66266949572207</v>
+        <v>4.86432089820986</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -648,7 +648,7 @@
         <v>1993</v>
       </c>
       <c s="7">
-        <v>32.6071272384155</v>
+        <v>32.7751144579642</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -659,7 +659,7 @@
         <v>1993</v>
       </c>
       <c s="7">
-        <v>1.03904092028466</v>
+        <v>1.03891819988547</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -670,7 +670,7 @@
         <v>1993</v>
       </c>
       <c s="7">
-        <v>13.6188198891184</v>
+        <v>13.618820614502</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -681,7 +681,7 @@
         <v>1993</v>
       </c>
       <c s="7">
-        <v>9.27404062296623</v>
+        <v>9.44765136204015</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -692,7 +692,7 @@
         <v>1993</v>
       </c>
       <c s="7">
-        <v>15.3491660386849</v>
+        <v>15.3499494216454</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -703,7 +703,7 @@
         <v>1994</v>
       </c>
       <c s="7">
-        <v>4.550449260861</v>
+        <v>4.75259320850404</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -714,7 +714,7 @@
         <v>1994</v>
       </c>
       <c s="7">
-        <v>34.0276345553664</v>
+        <v>34.1931306042555</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -725,7 +725,7 @@
         <v>1994</v>
       </c>
       <c s="7">
-        <v>1.25630367435227</v>
+        <v>1.25663264549478</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -736,7 +736,7 @@
         <v>1994</v>
       </c>
       <c s="7">
-        <v>12.3511421047486</v>
+        <v>12.3511430237696</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -747,7 +747,7 @@
         <v>1994</v>
       </c>
       <c s="7">
-        <v>9.17302520699467</v>
+        <v>9.34986911397677</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -758,7 +758,7 @@
         <v>1994</v>
       </c>
       <c s="7">
-        <v>15.3999666261701</v>
+        <v>15.4007771930409</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -769,7 +769,7 @@
         <v>1995</v>
       </c>
       <c s="7">
-        <v>4.34127879717928</v>
+        <v>4.54354258045082</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -780,7 +780,7 @@
         <v>1995</v>
       </c>
       <c s="7">
-        <v>35.6547530385613</v>
+        <v>35.8238955206585</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -791,7 +791,7 @@
         <v>1995</v>
       </c>
       <c s="7">
-        <v>1.53931620115292</v>
+        <v>1.54313022134207</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -802,7 +802,7 @@
         <v>1995</v>
       </c>
       <c s="7">
-        <v>13.5429413436551</v>
+        <v>13.5429421529511</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -813,7 +813,7 @@
         <v>1995</v>
       </c>
       <c s="7">
-        <v>9.25428431182129</v>
+        <v>9.46261791103032</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -824,7 +824,7 @@
         <v>1995</v>
       </c>
       <c s="7">
-        <v>15.6531658871954</v>
+        <v>15.6539789279543</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -835,7 +835,7 @@
         <v>1996</v>
       </c>
       <c s="7">
-        <v>4.25741773808109</v>
+        <v>4.45726530868295</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -846,7 +846,7 @@
         <v>1996</v>
       </c>
       <c s="7">
-        <v>36.3486297634791</v>
+        <v>36.5205564390714</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -857,7 +857,7 @@
         <v>1996</v>
       </c>
       <c s="7">
-        <v>1.68405533334949</v>
+        <v>1.68638371534395</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -868,7 +868,7 @@
         <v>1996</v>
       </c>
       <c s="7">
-        <v>14.469244537164</v>
+        <v>14.4692454624386</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -879,7 +879,7 @@
         <v>1996</v>
       </c>
       <c s="7">
-        <v>9.18025603401848</v>
+        <v>9.41654954917256</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -890,7 +890,7 @@
         <v>1996</v>
       </c>
       <c s="7">
-        <v>17.205745530998</v>
+        <v>17.2064957726051</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -901,7 +901,7 @@
         <v>1997</v>
       </c>
       <c s="7">
-        <v>4.06737336815941</v>
+        <v>4.26124423003695</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -912,7 +912,7 @@
         <v>1997</v>
       </c>
       <c s="7">
-        <v>38.6028257681942</v>
+        <v>38.7727791176104</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -923,7 +923,7 @@
         <v>1997</v>
       </c>
       <c s="7">
-        <v>1.71434780727059</v>
+        <v>1.71272132306938</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -934,7 +934,7 @@
         <v>1997</v>
       </c>
       <c s="7">
-        <v>12.9862611295357</v>
+        <v>12.9862648907183</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -945,7 +945,7 @@
         <v>1997</v>
       </c>
       <c s="7">
-        <v>9.16581406427467</v>
+        <v>9.43064811011162</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -956,7 +956,7 @@
         <v>1997</v>
       </c>
       <c s="7">
-        <v>16.2157111259679</v>
+        <v>16.2164455408983</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -967,7 +967,7 @@
         <v>1998</v>
       </c>
       <c s="7">
-        <v>3.85327939638098</v>
+        <v>4.04123445169698</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -978,7 +978,7 @@
         <v>1998</v>
       </c>
       <c s="7">
-        <v>36.3149939619068</v>
+        <v>36.4820909026203</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -989,7 +989,7 @@
         <v>1998</v>
       </c>
       <c s="7">
-        <v>1.52174475292629</v>
+        <v>1.52171569026477</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1000,7 +1000,7 @@
         <v>1998</v>
       </c>
       <c s="7">
-        <v>13.01591924754</v>
+        <v>13.0159250894313</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1011,7 +1011,7 @@
         <v>1998</v>
       </c>
       <c s="7">
-        <v>9.13228889852266</v>
+        <v>9.43305025648932</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1022,7 +1022,7 @@
         <v>1998</v>
       </c>
       <c s="7">
-        <v>18.2076989026269</v>
+        <v>18.2084408713982</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1033,7 +1033,7 @@
         <v>1999</v>
       </c>
       <c s="7">
-        <v>3.70500493639842</v>
+        <v>3.89100422548796</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1044,7 +1044,7 @@
         <v>1999</v>
       </c>
       <c s="7">
-        <v>35.0912562750712</v>
+        <v>35.2604577312255</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1055,7 +1055,7 @@
         <v>1999</v>
       </c>
       <c s="7">
-        <v>1.43434213314623</v>
+        <v>1.44162661586616</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1066,7 +1066,7 @@
         <v>1999</v>
       </c>
       <c s="7">
-        <v>13.6103596475562</v>
+        <v>13.6103722146606</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1077,7 +1077,7 @@
         <v>1999</v>
       </c>
       <c s="7">
-        <v>9.04256312080106</v>
+        <v>9.37294778253871</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1088,7 +1088,7 @@
         <v>1999</v>
       </c>
       <c s="7">
-        <v>17.5841168681294</v>
+        <v>17.5848021957132</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1099,7 +1099,7 @@
         <v>2000</v>
       </c>
       <c s="7">
-        <v>3.5695667631904</v>
+        <v>3.75604584125314</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1110,7 +1110,7 @@
         <v>2000</v>
       </c>
       <c s="7">
-        <v>35.9764693769114</v>
+        <v>36.1726126507832</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1121,7 +1121,7 @@
         <v>2000</v>
       </c>
       <c s="7">
-        <v>1.35993717749074</v>
+        <v>1.36972544144925</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1132,7 +1132,7 @@
         <v>2000</v>
       </c>
       <c s="7">
-        <v>12.4057041519197</v>
+        <v>12.4057182994038</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1143,7 +1143,7 @@
         <v>2000</v>
       </c>
       <c s="7">
-        <v>8.83318478243993</v>
+        <v>9.18881622497159</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1154,7 +1154,7 @@
         <v>2000</v>
       </c>
       <c s="7">
-        <v>18.4955540921841</v>
+        <v>18.4958457284814</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1165,7 +1165,7 @@
         <v>2001</v>
       </c>
       <c s="7">
-        <v>3.45923092091472</v>
+        <v>3.64239157754398</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1176,7 +1176,7 @@
         <v>2001</v>
       </c>
       <c s="7">
-        <v>37.2668660686698</v>
+        <v>37.4647784144556</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1187,7 +1187,7 @@
         <v>2001</v>
       </c>
       <c s="7">
-        <v>1.57516042480224</v>
+        <v>1.58845503674828</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1198,7 +1198,7 @@
         <v>2001</v>
       </c>
       <c s="7">
-        <v>13.6093394756561</v>
+        <v>13.6093427713046</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1209,7 +1209,7 @@
         <v>2001</v>
       </c>
       <c s="7">
-        <v>8.78309939926801</v>
+        <v>9.14389809706377</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1220,7 +1220,7 @@
         <v>2001</v>
       </c>
       <c s="7">
-        <v>19.8304733175642</v>
+        <v>19.8294976848064</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1231,7 +1231,7 @@
         <v>2002</v>
       </c>
       <c s="7">
-        <v>3.52708477213667</v>
+        <v>3.72468423195662</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1242,7 +1242,7 @@
         <v>2002</v>
       </c>
       <c s="7">
-        <v>37.5978153184601</v>
+        <v>37.7919979980668</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1253,7 +1253,7 @@
         <v>2002</v>
       </c>
       <c s="7">
-        <v>1.69505678638989</v>
+        <v>1.6977772012544</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1264,7 +1264,7 @@
         <v>2002</v>
       </c>
       <c s="7">
-        <v>12.8814346510309</v>
+        <v>12.8814362610749</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1275,7 +1275,7 @@
         <v>2002</v>
       </c>
       <c s="7">
-        <v>8.61286112594014</v>
+        <v>8.98437398508298</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1286,7 +1286,7 @@
         <v>2002</v>
       </c>
       <c s="7">
-        <v>21.9646623057205</v>
+        <v>21.9624847228686</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1297,7 +1297,7 @@
         <v>2003</v>
       </c>
       <c s="7">
-        <v>3.58108411950569</v>
+        <v>3.7753613512546</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1308,7 +1308,7 @@
         <v>2003</v>
       </c>
       <c s="7">
-        <v>40.5968756030745</v>
+        <v>40.7905881716675</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1319,7 +1319,7 @@
         <v>2003</v>
       </c>
       <c s="7">
-        <v>1.732104854962</v>
+        <v>1.72872956931644</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1330,7 +1330,7 @@
         <v>2003</v>
       </c>
       <c s="7">
-        <v>13.5646356989359</v>
+        <v>13.5646371374039</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1341,7 +1341,7 @@
         <v>2003</v>
       </c>
       <c s="7">
-        <v>8.44552267869171</v>
+        <v>8.83138430524631</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1352,7 +1352,7 @@
         <v>2003</v>
       </c>
       <c s="7">
-        <v>23.7270653595088</v>
+        <v>23.7236700438734</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1363,7 +1363,7 @@
         <v>2004</v>
       </c>
       <c s="7">
-        <v>3.74381967890489</v>
+        <v>3.93756913795169</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1374,7 +1374,7 @@
         <v>2004</v>
       </c>
       <c s="7">
-        <v>40.2311078119067</v>
+        <v>40.4352427616138</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1385,7 +1385,7 @@
         <v>2004</v>
       </c>
       <c s="7">
-        <v>1.76804953240545</v>
+        <v>1.76350516207955</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1396,7 +1396,7 @@
         <v>2004</v>
       </c>
       <c s="7">
-        <v>13.0273991187326</v>
+        <v>13.0274004426558</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1407,7 +1407,7 @@
         <v>2004</v>
       </c>
       <c s="7">
-        <v>8.42700908134635</v>
+        <v>8.80963540113583</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1418,7 +1418,7 @@
         <v>2004</v>
       </c>
       <c s="7">
-        <v>24.2455563896384</v>
+        <v>24.2411020355385</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1429,7 +1429,7 @@
         <v>2005</v>
       </c>
       <c s="7">
-        <v>3.54350124280076</v>
+        <v>3.72584517621561</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1440,7 +1440,7 @@
         <v>2005</v>
       </c>
       <c s="7">
-        <v>41.5737653853068</v>
+        <v>41.7625899519644</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1451,7 +1451,7 @@
         <v>2005</v>
       </c>
       <c s="7">
-        <v>1.79412621114735</v>
+        <v>1.78192785028903</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1462,7 +1462,7 @@
         <v>2005</v>
       </c>
       <c s="7">
-        <v>12.740533553138</v>
+        <v>12.7405334269002</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1473,7 +1473,7 @@
         <v>2005</v>
       </c>
       <c s="7">
-        <v>8.33918432123197</v>
+        <v>8.72099222451952</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1484,7 +1484,7 @@
         <v>2005</v>
       </c>
       <c s="7">
-        <v>24.6139575724316</v>
+        <v>24.6088283357966</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1495,7 +1495,7 @@
         <v>2006</v>
       </c>
       <c s="7">
-        <v>3.53556735981294</v>
+        <v>3.70316707528359</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1506,7 +1506,7 @@
         <v>2006</v>
       </c>
       <c s="7">
-        <v>40.7566901317046</v>
+        <v>40.9302758426506</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1517,7 +1517,7 @@
         <v>2006</v>
       </c>
       <c s="7">
-        <v>1.77360687125006</v>
+        <v>1.76410983842361</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1528,7 +1528,7 @@
         <v>2006</v>
       </c>
       <c s="7">
-        <v>12.6038875035694</v>
+        <v>12.603887320319</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1539,7 +1539,7 @@
         <v>2006</v>
       </c>
       <c s="7">
-        <v>8.28198054463852</v>
+        <v>8.6636589960769</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1550,7 +1550,7 @@
         <v>2006</v>
       </c>
       <c s="7">
-        <v>23.2413630677382</v>
+        <v>23.2348356361772</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1561,7 +1561,7 @@
         <v>2007</v>
       </c>
       <c s="7">
-        <v>3.39696631208866</v>
+        <v>3.56498229351837</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1572,7 +1572,7 @@
         <v>2007</v>
       </c>
       <c s="7">
-        <v>39.8471802320297</v>
+        <v>40.0212345834826</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1583,7 +1583,7 @@
         <v>2007</v>
       </c>
       <c s="7">
-        <v>1.81178400913036</v>
+        <v>1.82850183055417</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1594,7 +1594,7 @@
         <v>2007</v>
       </c>
       <c s="7">
-        <v>10.6162353779968</v>
+        <v>10.6162351023082</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1605,7 +1605,7 @@
         <v>2007</v>
       </c>
       <c s="7">
-        <v>8.31358307007608</v>
+        <v>8.63102996125579</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1616,7 +1616,7 @@
         <v>2007</v>
       </c>
       <c s="7">
-        <v>23.4441882393914</v>
+        <v>23.435069945799</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1627,7 +1627,7 @@
         <v>2008</v>
       </c>
       <c s="7">
-        <v>3.27406433653898</v>
+        <v>3.44254600231664</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1638,7 +1638,7 @@
         <v>2008</v>
       </c>
       <c s="7">
-        <v>40.3031539657976</v>
+        <v>40.4792122731365</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1649,7 +1649,7 @@
         <v>2008</v>
       </c>
       <c s="7">
-        <v>1.83874050208631</v>
+        <v>1.86692680828826</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1660,7 +1660,7 @@
         <v>2008</v>
       </c>
       <c s="7">
-        <v>10.9272169171262</v>
+        <v>10.9272165544865</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1671,7 +1671,7 @@
         <v>2008</v>
       </c>
       <c s="7">
-        <v>8.50119608826265</v>
+        <v>8.80755844464533</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1682,7 +1682,7 @@
         <v>2008</v>
       </c>
       <c s="7">
-        <v>21.9968047790726</v>
+        <v>21.986356545954</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1693,7 +1693,7 @@
         <v>2009</v>
       </c>
       <c s="7">
-        <v>3.29335016382451</v>
+        <v>3.45870295946472</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1704,7 +1704,7 @@
         <v>2009</v>
       </c>
       <c s="7">
-        <v>35.3758119164849</v>
+        <v>35.5733210222206</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1715,7 +1715,7 @@
         <v>2009</v>
       </c>
       <c s="7">
-        <v>1.70817543647484</v>
+        <v>1.72797732247767</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1726,7 +1726,7 @@
         <v>2009</v>
       </c>
       <c s="7">
-        <v>10.0672081222135</v>
+        <v>10.0672077227489</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1737,7 +1737,7 @@
         <v>2009</v>
       </c>
       <c s="7">
-        <v>8.41059058692525</v>
+        <v>8.71234393954871</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1748,7 +1748,7 @@
         <v>2009</v>
       </c>
       <c s="7">
-        <v>21.3676304809703</v>
+        <v>21.3566142618534</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1759,7 +1759,7 @@
         <v>2010</v>
       </c>
       <c s="7">
-        <v>3.18938628862972</v>
+        <v>3.35150102083395</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1770,7 +1770,7 @@
         <v>2010</v>
       </c>
       <c s="7">
-        <v>39.0808360701092</v>
+        <v>39.2701938578686</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1781,7 +1781,7 @@
         <v>2010</v>
       </c>
       <c s="7">
-        <v>1.85420207547392</v>
+        <v>1.87589485161698</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1792,7 +1792,7 @@
         <v>2010</v>
       </c>
       <c s="7">
-        <v>10.2521051453206</v>
+        <v>10.2521047156424</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1803,7 +1803,7 @@
         <v>2010</v>
       </c>
       <c s="7">
-        <v>8.26576121660741</v>
+        <v>8.55274871289271</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1814,7 +1814,7 @@
         <v>2010</v>
       </c>
       <c s="7">
-        <v>22.1508775529763</v>
+        <v>22.1394718738072</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1825,7 +1825,7 @@
         <v>2011</v>
       </c>
       <c s="7">
-        <v>3.12890949030421</v>
+        <v>3.29014105906704</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1836,7 +1836,7 @@
         <v>2011</v>
       </c>
       <c s="7">
-        <v>38.8009467263228</v>
+        <v>38.9861218595763</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1847,7 +1847,7 @@
         <v>2011</v>
       </c>
       <c s="7">
-        <v>1.91395238815485</v>
+        <v>1.94113014856608</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1858,7 +1858,7 @@
         <v>2011</v>
       </c>
       <c s="7">
-        <v>8.98608651546959</v>
+        <v>8.98608803547929</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1869,7 +1869,7 @@
         <v>2011</v>
       </c>
       <c s="7">
-        <v>8.38767993885728</v>
+        <v>8.66955624802438</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1880,7 +1880,7 @@
         <v>2011</v>
       </c>
       <c s="7">
-        <v>21.3891459390555</v>
+        <v>21.3775098959428</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1891,7 +1891,7 @@
         <v>2012</v>
       </c>
       <c s="7">
-        <v>3.03307407816506</v>
+        <v>3.19337114537961</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1902,7 +1902,7 @@
         <v>2012</v>
       </c>
       <c s="7">
-        <v>36.6692054491822</v>
+        <v>36.8774824818404</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1913,7 +1913,7 @@
         <v>2012</v>
       </c>
       <c s="7">
-        <v>1.98204618772677</v>
+        <v>1.97909782606955</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1924,7 +1924,7 @@
         <v>2012</v>
       </c>
       <c s="7">
-        <v>8.63680227485381</v>
+        <v>8.60880138066907</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -1935,7 +1935,7 @@
         <v>2012</v>
       </c>
       <c s="7">
-        <v>8.25371121991475</v>
+        <v>8.52584395555114</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -1946,7 +1946,7 @@
         <v>2012</v>
       </c>
       <c s="7">
-        <v>21.3141695910234</v>
+        <v>21.3025146059239</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -1957,7 +1957,7 @@
         <v>2013</v>
       </c>
       <c s="7">
-        <v>2.87828851917596</v>
+        <v>3.03817710347073</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -1968,7 +1968,7 @@
         <v>2013</v>
       </c>
       <c s="7">
-        <v>35.922066563687</v>
+        <v>36.1032411998416</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -1979,7 +1979,7 @@
         <v>2013</v>
       </c>
       <c s="7">
-        <v>2.04639800015329</v>
+        <v>2.01576983537276</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -1990,7 +1990,7 @@
         <v>2013</v>
       </c>
       <c s="7">
-        <v>8.87898598442696</v>
+        <v>8.87899314867744</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2001,7 +2001,7 @@
         <v>2013</v>
       </c>
       <c s="7">
-        <v>8.24158015834714</v>
+        <v>8.50047114424834</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2012,7 +2012,7 @@
         <v>2013</v>
       </c>
       <c s="7">
-        <v>22.3425808337111</v>
+        <v>22.3310938086857</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2023,7 +2023,7 @@
         <v>2014</v>
       </c>
       <c s="7">
-        <v>2.82326071711176</v>
+        <v>2.98290985665106</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2034,7 +2034,7 @@
         <v>2014</v>
       </c>
       <c s="7">
-        <v>33.7399246000278</v>
+        <v>33.9167314150813</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2045,7 +2045,7 @@
         <v>2014</v>
       </c>
       <c s="7">
-        <v>2.13386734392502</v>
+        <v>2.05087972557409</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2056,7 +2056,7 @@
         <v>2014</v>
       </c>
       <c s="7">
-        <v>7.81144948004674</v>
+        <v>7.81145928343011</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2067,7 +2067,7 @@
         <v>2014</v>
       </c>
       <c s="7">
-        <v>8.45499206399607</v>
+        <v>8.70669250194535</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2078,7 +2078,7 @@
         <v>2014</v>
       </c>
       <c s="7">
-        <v>21.7578111804899</v>
+        <v>21.7464916182172</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2089,7 +2089,7 @@
         <v>2015</v>
       </c>
       <c s="7">
-        <v>2.74434952808983</v>
+        <v>2.90398192223115</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2100,7 +2100,7 @@
         <v>2015</v>
       </c>
       <c s="7">
-        <v>35.1713940303362</v>
+        <v>35.3509913219033</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2111,7 +2111,7 @@
         <v>2015</v>
       </c>
       <c s="7">
-        <v>2.22654539820589</v>
+        <v>2.07428191236102</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2122,7 +2122,7 @@
         <v>2015</v>
       </c>
       <c s="7">
-        <v>8.22551361527332</v>
+        <v>8.22552803725222</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2133,7 +2133,7 @@
         <v>2015</v>
       </c>
       <c s="7">
-        <v>8.41472475628275</v>
+        <v>8.66296499425589</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2144,7 +2144,7 @@
         <v>2015</v>
       </c>
       <c s="7">
-        <v>22.1521230709824</v>
+        <v>22.1412355065636</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2155,7 +2155,7 @@
         <v>2016</v>
       </c>
       <c s="7">
-        <v>2.72012367055508</v>
+        <v>2.8905489057984</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2166,7 +2166,7 @@
         <v>2016</v>
       </c>
       <c s="7">
-        <v>34.7652800435203</v>
+        <v>34.9596296830031</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2177,7 +2177,7 @@
         <v>2016</v>
       </c>
       <c s="7">
-        <v>2.28469380394359</v>
+        <v>2.15654869283072</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2188,7 +2188,7 @@
         <v>2016</v>
       </c>
       <c s="7">
-        <v>8.45664436924839</v>
+        <v>8.45665735857166</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2199,7 +2199,7 @@
         <v>2016</v>
       </c>
       <c s="7">
-        <v>8.6100275635281</v>
+        <v>8.85786071543435</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2210,7 +2210,7 @@
         <v>2016</v>
       </c>
       <c s="7">
-        <v>23.0264605955942</v>
+        <v>22.9981520683799</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2221,7 +2221,7 @@
         <v>2017</v>
       </c>
       <c s="7">
-        <v>2.56313438538979</v>
+        <v>2.73044959428287</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2232,7 +2232,7 @@
         <v>2017</v>
       </c>
       <c s="7">
-        <v>36.4855301142795</v>
+        <v>36.6919854169288</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2243,7 +2243,7 @@
         <v>2017</v>
       </c>
       <c s="7">
-        <v>2.3207393766964</v>
+        <v>2.19932738989157</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2254,7 +2254,7 @@
         <v>2017</v>
       </c>
       <c s="7">
-        <v>8.62431357556412</v>
+        <v>8.62432179069952</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2265,7 +2265,7 @@
         <v>2017</v>
       </c>
       <c s="7">
-        <v>8.49837097277567</v>
+        <v>8.72959732780551</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2276,7 +2276,7 @@
         <v>2017</v>
       </c>
       <c s="7">
-        <v>23.7032618396032</v>
+        <v>23.6596795469087</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2287,7 +2287,7 @@
         <v>2018</v>
       </c>
       <c s="7">
-        <v>2.43357774876217</v>
+        <v>2.60211389189099</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2298,7 +2298,7 @@
         <v>2018</v>
       </c>
       <c s="7">
-        <v>34.0242622777726</v>
+        <v>34.2261987143675</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2309,7 +2309,7 @@
         <v>2018</v>
       </c>
       <c s="7">
-        <v>2.3332802917903</v>
+        <v>2.29014363591542</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2320,7 +2320,7 @@
         <v>2018</v>
       </c>
       <c s="7">
-        <v>7.87343223194989</v>
+        <v>7.87343736152852</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2331,7 +2331,7 @@
         <v>2018</v>
       </c>
       <c s="7">
-        <v>8.37281832126479</v>
+        <v>8.6213201407532</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2342,7 +2342,7 @@
         <v>2018</v>
       </c>
       <c s="7">
-        <v>23.8660749958356</v>
+        <v>23.8282803492221</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2353,7 +2353,7 @@
         <v>2019</v>
       </c>
       <c s="7">
-        <v>2.37692371627802</v>
+        <v>2.54423080680594</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2364,7 +2364,7 @@
         <v>2019</v>
       </c>
       <c s="7">
-        <v>35.0735809859856</v>
+        <v>35.2790473131182</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2375,7 +2375,7 @@
         <v>2019</v>
       </c>
       <c s="7">
-        <v>2.25236677997598</v>
+        <v>2.24678799108953</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2386,7 +2386,7 @@
         <v>2019</v>
       </c>
       <c s="7">
-        <v>8.09105941830482</v>
+        <v>8.09106317995447</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2397,7 +2397,7 @@
         <v>2019</v>
       </c>
       <c s="7">
-        <v>8.30431332132344</v>
+        <v>8.55928381848269</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2408,7 +2408,7 @@
         <v>2019</v>
       </c>
       <c s="7">
-        <v>23.9600061748608</v>
+        <v>23.9202550389451</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2419,7 +2419,7 @@
         <v>2020</v>
       </c>
       <c s="7">
-        <v>2.31022706561171</v>
+        <v>2.47835824736419</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2430,7 +2430,7 @@
         <v>2020</v>
       </c>
       <c s="7">
-        <v>32.5024395824216</v>
+        <v>32.6977150408037</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2441,7 +2441,7 @@
         <v>2020</v>
       </c>
       <c s="7">
-        <v>2.14319833548577</v>
+        <v>2.19416435223118</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2452,7 +2452,7 @@
         <v>2020</v>
       </c>
       <c s="7">
-        <v>8.08586227972943</v>
+        <v>8.08592704721839</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2463,7 +2463,7 @@
         <v>2020</v>
       </c>
       <c s="7">
-        <v>8.27587887588561</v>
+        <v>8.54753967878758</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2474,7 +2474,7 @@
         <v>2020</v>
       </c>
       <c s="7">
-        <v>20.7124497197921</v>
+        <v>20.6750843325077</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2485,7 +2485,7 @@
         <v>2021</v>
       </c>
       <c s="7">
-        <v>2.29516159283896</v>
+        <v>2.46088134781384</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2496,7 +2496,7 @@
         <v>2021</v>
       </c>
       <c s="7">
-        <v>34.495884458099</v>
+        <v>34.7048563612635</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2507,7 +2507,7 @@
         <v>2021</v>
       </c>
       <c s="7">
-        <v>1.83722930680702</v>
+        <v>1.96164466063353</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2518,7 +2518,7 @@
         <v>2021</v>
       </c>
       <c s="7">
-        <v>8.86322351605047</v>
+        <v>8.80215237343746</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2529,7 +2529,7 @@
         <v>2021</v>
       </c>
       <c s="7">
-        <v>8.29260528429694</v>
+        <v>8.57758819691323</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2540,7 +2540,7 @@
         <v>2021</v>
       </c>
       <c s="7">
-        <v>21.5756609510986</v>
+        <v>21.5661268870435</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2551,7 +2551,7 @@
         <v>2022</v>
       </c>
       <c s="7">
-        <v>2.21785146219083</v>
+        <v>2.38295228865568</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2562,7 +2562,7 @@
         <v>2022</v>
       </c>
       <c s="7">
-        <v>32.6268261519574</v>
+        <v>32.7160072735995</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2573,7 +2573,7 @@
         <v>2022</v>
       </c>
       <c s="7">
-        <v>1.81641946037382</v>
+        <v>1.90853146732953</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2584,7 +2584,7 @@
         <v>2022</v>
       </c>
       <c s="7">
-        <v>7.37810562857693</v>
+        <v>7.3426156924643</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2595,7 +2595,7 @@
         <v>2022</v>
       </c>
       <c s="7">
-        <v>8.21700103260333</v>
+        <v>8.52322156664051</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2606,7 +2606,7 @@
         <v>2022</v>
       </c>
       <c s="7">
-        <v>20.5878129435322</v>
+        <v>20.6418227012083</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
@@ -2617,7 +2617,7 @@
         <v>2023</v>
       </c>
       <c s="7">
-        <v>2.1725970477598</v>
+        <v>2.40745077932201</v>
       </c>
       <c t="str">
         <v>Abfallwirtschaft</v>
@@ -2628,7 +2628,7 @@
         <v>2023</v>
       </c>
       <c s="7">
-        <v>30.3766603244059</v>
+        <v>29.8979182816958</v>
       </c>
       <c t="str">
         <v>Energie &amp; Industrie mit Emissionshandel</v>
@@ -2639,7 +2639,7 @@
         <v>2023</v>
       </c>
       <c s="7">
-        <v>1.77978293099295</v>
+        <v>1.81795611153452</v>
       </c>
       <c t="str">
         <v>F-Gase</v>
@@ -2650,7 +2650,7 @@
         <v>2023</v>
       </c>
       <c s="7">
-        <v>5.88570136580868</v>
+        <v>6.33320212467772</v>
       </c>
       <c t="str">
         <v>Gebäude</v>
@@ -2661,7 +2661,7 @@
         <v>2023</v>
       </c>
       <c s="7">
-        <v>8.14108422826879</v>
+        <v>8.39411157724551</v>
       </c>
       <c t="str">
         <v>Landwirtschaft</v>
@@ -2672,7 +2672,73 @@
         <v>2023</v>
       </c>
       <c s="7">
-        <v>19.813768214392</v>
+        <v>19.8452844283511</v>
+      </c>
+      <c t="str">
+        <v>Verkehr (inkl. nationalem Flugverkehr)</v>
+      </c>
+    </row>
+    <row r="208">
+      <c s="6">
+        <v>2024</v>
+      </c>
+      <c s="7">
+        <v>2.35982325667732</v>
+      </c>
+      <c t="str">
+        <v>Abfallwirtschaft</v>
+      </c>
+    </row>
+    <row r="209">
+      <c s="6">
+        <v>2024</v>
+      </c>
+      <c s="7">
+        <v>29.3188410915582</v>
+      </c>
+      <c t="str">
+        <v>Energie &amp; Industrie mit Emissionshandel</v>
+      </c>
+    </row>
+    <row r="210">
+      <c s="6">
+        <v>2024</v>
+      </c>
+      <c s="7">
+        <v>1.71000168843608</v>
+      </c>
+      <c t="str">
+        <v>F-Gase</v>
+      </c>
+    </row>
+    <row r="211">
+      <c s="6">
+        <v>2024</v>
+      </c>
+      <c s="7">
+        <v>5.91713099482536</v>
+      </c>
+      <c t="str">
+        <v>Gebäude</v>
+      </c>
+    </row>
+    <row r="212">
+      <c s="6">
+        <v>2024</v>
+      </c>
+      <c s="7">
+        <v>8.33026150483861</v>
+      </c>
+      <c t="str">
+        <v>Landwirtschaft</v>
+      </c>
+    </row>
+    <row r="213">
+      <c s="6">
+        <v>2024</v>
+      </c>
+      <c s="7">
+        <v>19.3038030879913</v>
       </c>
       <c t="str">
         <v>Verkehr (inkl. nationalem Flugverkehr)</v>
